--- a/data/04_OverseasExp.xlsx
+++ b/data/04_OverseasExp.xlsx
@@ -7,11 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_OverseasExp" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'04_OverseasExp'!$A$1:$F$1</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -19,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,26 +25,16 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="000078D4"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -54,32 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00CCCCCC"/>
-      </left>
-      <right style="thin">
-        <color rgb="00CCCCCC"/>
-      </right>
-      <top style="thin">
-        <color rgb="00CCCCCC"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00CCCCCC"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -445,261 +413,1302 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="35" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>OverseasId</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>EmployeeId</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Purpose</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>StartDate</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>EndDate</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>EMP001</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>EMP020</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>베트남</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>유럽 시장조사 및 파트너 발굴</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2023-02-01</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2024-01-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>EMP020</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>싱가포르</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>해외법인 경영관리 파견</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2024-02-01</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>EMP033</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>사우디아라비아</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Global Sales Conference 참석 및 거래처 미팅</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2020-04-01</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2023-03-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>EMP035</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>독일</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>미국 Dow Chemical 공정 연수</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2022-03-01</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2022-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>EMP037</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>인도네시아</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ETH Zurich 촉매연구 프로그램</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2023-04-01</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2024-03-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>EMP037</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>MIT Chemical Engineering 공동연구</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2023-02-01</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2023-07-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>EMP040</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>중국 화학산업 시장조사</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>EMP040</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>프랑스</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Wharton Executive Program</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2021-04-01</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2022-03-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>EMP042</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>사우디아라비아</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>동남아 시장개척 파견</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2019-02-01</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2022-01-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>EMP043</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>독일</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Global Sales Conference 참석 및 거래처 미팅</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2024-07-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>EMP046</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>베트남</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>INSEAD Global Leadership Program 수료</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>EMP047</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Technical University of Munich 공정개발 연수</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>EMP047</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>영국</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Stanford Materials Science 연수</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>EMP048</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>베트남</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>해외법인 경영관리 파견</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2020-02-01</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2020-07-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>EMP052</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>싱가포르</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Global Sales Conference 참석 및 거래처 미팅</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2020-02-01</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2022-01-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>EMP052</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>독일</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>INSEAD Global Leadership Program 수료</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2022-06-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>EMP056</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
         <is>
           <t>미국</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Stanford HR Leaders Program 수료</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>2018-06-01</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>2018-08-31</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>EMP003</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>중국</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>상하이 JV 주재원 (법무/경영지원)</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>2012-01-01</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>2014-12-31</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>EMP003</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>미국</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>University of Michigan MBA 과정</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2013-08-01</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2015-05-31</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>EMP005</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Global Sales Conference 참석 및 거래처 미팅</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2021-06-01</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2021-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>EMP056</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>베트남</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>중국 화학산업 시장조사</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2020-05-01</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2021-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>EMP058</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>싱가포르</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Georgia Tech 고분자연구 공동프로젝트</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2023-05-01</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2023-07-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>EMP058</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>사우디아라비아</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Technical University of Munich 공정개발 연수</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2016-04-01</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2019-03-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>EMP059</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>프랑스</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>사우디 SABIC JV 파견</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2017-02-01</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2020-01-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>EMP059</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>프랑스</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>일본 미쓰비시케미칼 기술교류</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2020-05-01</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2020-07-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>EMP061</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Stanford Materials Science 연수</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2019-04-01</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2019-09-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>EMP066</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>영국</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>독일 BASF 공장 벤치마킹</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2018-02-01</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2018-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>EMP068</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>인도네시아</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>일본 미쓰비시케미칼 기술교류</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2010-03-01</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2010-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>EMP078</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>프랑스</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>해외법인 경영관리 파견</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2017-05-01</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2019-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>EMP078</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>동남아 시장개척 파견</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2023-05-01</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2023-10-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>EMP080</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>프랑스</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>유럽 시장조사 및 파트너 발굴</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2020-02-01</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2020-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>EMP080</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>영국</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Wharton Executive Program</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2013-01-01</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2013-04-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>EMP081</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>유럽 시장조사 및 파트너 발굴</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2012-04-01</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2012-09-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>EMP081</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>인도네시아</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>유럽 시장조사 및 파트너 발굴</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>2010-05-01</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2013-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>EMP083</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>인도네시아</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>유럽 시장조사 및 파트너 발굴</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2008-05-01</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2010-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>EMP091</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>영국</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>일본 미쓰비시케미칼 기술교류</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>2012-02-01</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2014-01-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>EMP093</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>사우디아라비아</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>해외법인 경영관리 파견</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2005-05-01</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2005-07-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>EMP093</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>베트남</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Global Sales Conference 참석 및 거래처 미팅</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>2021-04-01</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2021-06-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>EMP096</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
         <is>
           <t>독일</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>글로벌 마케팅 벤치마킹 파견</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>해외법인 경영관리 파견</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>2020-03-01</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2023-02-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>EMP096</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>사우디아라비아</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>동남아 시장개척 파견</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>EMP097</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>영국</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Tsinghua University 신소재 연구교류</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2008-05-01</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2010-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>EMP097</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>베트남</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Technical University of Munich 공정개발 연수</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2007-05-01</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2008-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>EMP099</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>인도네시아</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>INSEAD Global Leadership Program 수료</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>EMP099</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>동남아 시장개척 파견</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2024-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>EMP100</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>독일</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>해외법인 경영관리 파견</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
         <is>
           <t>2017-03-01</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>2017-08-31</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>EMP007</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>일본</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>도쿄 주재원 (해외영업)</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2013-01-01</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2017-12-31</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>EMP009</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>미국</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Wharton MBA 과정</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2006-08-01</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2008-05-31</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>EMP009</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>싱가포르</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>APAC 전략회의 장기 파견</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>2016-01-01</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2016-06-30</t>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2019-02-19</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>